--- a/Pedidos/Pedidos-modelo.xlsx
+++ b/Pedidos/Pedidos-modelo.xlsx
@@ -948,7 +948,7 @@
     <t xml:space="preserve">Cliente por telefone · Telefone</t>
   </si>
   <si>
-    <t xml:space="preserve">Uma pizza grande meia calabresa, meia mussarela.</t>
+    <t xml:space="preserve">Uma pizza grande meia calabresa, meia muçarela.</t>
   </si>
   <si>
     <t xml:space="preserve">Complemento do endereço pedido e lido de volta antes de confirmar.</t>
@@ -963,7 +963,7 @@
     <t xml:space="preserve">Cliente pelo aplicativo · Aplicativo</t>
   </si>
   <si>
-    <t xml:space="preserve">Pizza de mussarela “sem glúten”, para uma criança celíaca. Isenção total de glúten, inclusive de contaminação na cozinha.</t>
+    <t xml:space="preserve">Pizza de muçarela “sem glúten”, para uma criança celíaca. Isenção total de glúten, inclusive de contaminação na cozinha.</t>
   </si>
   <si>
     <t xml:space="preserve">A cozinha não garante a ausência de glúten. Cliente informado pelo telefone, com o motivo.</t>
@@ -987,7 +987,7 @@
     <t xml:space="preserve">20 pizzas para segunda 29/03, às 11h.</t>
   </si>
   <si>
-    <t xml:space="preserve">A loja não abre às segundas, e o horário de encomenda começa às 18h. O cliente não aceitou outro dia.</t>
+    <t xml:space="preserve">A loja não atende encomendas para eventos às segundas, e o horário de encomenda começa às 18h. O cliente não aceitou outro dia.</t>
   </si>
   <si>
     <t xml:space="preserve">T-1201</t>
@@ -1855,11 +1855,11 @@
         </c:ser>
         <c:gapWidth val="60"/>
         <c:overlap val="0"/>
-        <c:axId val="71007288"/>
-        <c:axId val="98856317"/>
+        <c:axId val="16120322"/>
+        <c:axId val="88208181"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="71007288"/>
+        <c:axId val="16120322"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -1891,7 +1891,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="98856317"/>
+        <c:crossAx val="88208181"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1899,7 +1899,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="98856317"/>
+        <c:axId val="88208181"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -1939,7 +1939,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="71007288"/>
+        <c:crossAx val="16120322"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="1"/>
@@ -7778,7 +7778,7 @@
         <v>OK</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="32" t="s">
         <v>259</v>
       </c>
